--- a/artfynd/A 7213-2026 artfynd.xlsx
+++ b/artfynd/A 7213-2026 artfynd.xlsx
@@ -2809,7 +2809,7 @@
         <v>131674865</v>
       </c>
       <c r="B23" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 7213-2026 artfynd.xlsx
+++ b/artfynd/A 7213-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131674891</v>
+        <v>135298255</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459200</v>
+        <v>459206</v>
       </c>
       <c r="R2" t="n">
-        <v>6783838</v>
+        <v>6783780</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,64 +766,84 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131674892</v>
+        <v>135298260</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459218</v>
+        <v>459206</v>
       </c>
       <c r="R3" t="n">
-        <v>6783873</v>
+        <v>6783812</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +867,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -853,64 +893,84 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131674893</v>
+        <v>135298269</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459231</v>
+        <v>459172</v>
       </c>
       <c r="R4" t="n">
-        <v>6783873</v>
+        <v>6783876</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,12 +994,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -950,23 +1020,43 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131674894</v>
+        <v>131674891</v>
       </c>
       <c r="B5" t="n">
         <v>79373</v>
@@ -1001,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459258</v>
+        <v>459200</v>
       </c>
       <c r="R5" t="n">
-        <v>6783870</v>
+        <v>6783838</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131674895</v>
+        <v>131674892</v>
       </c>
       <c r="B6" t="n">
         <v>79373</v>
@@ -1098,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459235</v>
+        <v>459218</v>
       </c>
       <c r="R6" t="n">
-        <v>6783794</v>
+        <v>6783873</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131674896</v>
+        <v>131674893</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1195,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459194</v>
+        <v>459231</v>
       </c>
       <c r="R7" t="n">
-        <v>6783789</v>
+        <v>6783873</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131674897</v>
+        <v>131674894</v>
       </c>
       <c r="B8" t="n">
         <v>79373</v>
@@ -1292,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459178</v>
+        <v>459258</v>
       </c>
       <c r="R8" t="n">
-        <v>6783796</v>
+        <v>6783870</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,48 +1444,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131674865</v>
+        <v>131674895</v>
       </c>
       <c r="B9" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459284</v>
+        <v>459235</v>
       </c>
       <c r="R9" t="n">
-        <v>6783888</v>
+        <v>6783794</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1436,7 +1523,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1448,39 +1534,39 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131674771</v>
+        <v>131674896</v>
       </c>
       <c r="B10" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1490,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459199</v>
+        <v>459194</v>
       </c>
       <c r="R10" t="n">
-        <v>6783825</v>
+        <v>6783789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,53 +1638,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131674822</v>
+        <v>131674897</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459276</v>
+        <v>459178</v>
       </c>
       <c r="R11" t="n">
-        <v>6783886</v>
+        <v>6783796</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,42 +1735,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131674823</v>
+        <v>131674865</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>79130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1700,10 +1773,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459255</v>
+        <v>459284</v>
       </c>
       <c r="R12" t="n">
-        <v>6783871</v>
+        <v>6783888</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1744,6 +1817,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1755,60 +1829,52 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131674824</v>
+        <v>131674771</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459194</v>
+        <v>459199</v>
       </c>
       <c r="R13" t="n">
-        <v>6783789</v>
+        <v>6783825</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,7 +1933,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131674825</v>
+        <v>131674822</v>
       </c>
       <c r="B14" t="n">
         <v>57972</v>
@@ -1900,7 +1966,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1910,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459186</v>
+        <v>459276</v>
       </c>
       <c r="R14" t="n">
-        <v>6783788</v>
+        <v>6783886</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1972,27 +2038,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131674785</v>
+        <v>131674823</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2015,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459269</v>
+        <v>459255</v>
       </c>
       <c r="R15" t="n">
-        <v>6783881</v>
+        <v>6783871</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,34 +2136,34 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131674786</v>
+        <v>131674824</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2110,7 +2176,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2120,10 +2186,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459276</v>
+        <v>459194</v>
       </c>
       <c r="R16" t="n">
-        <v>6783842</v>
+        <v>6783789</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2182,27 +2248,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131674787</v>
+        <v>131674825</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2215,7 +2281,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2225,10 +2291,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459258</v>
+        <v>459186</v>
       </c>
       <c r="R17" t="n">
-        <v>6783805</v>
+        <v>6783788</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2287,32 +2353,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131674800</v>
+        <v>131674785</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2320,7 +2386,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2330,10 +2396,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459169</v>
+        <v>459269</v>
       </c>
       <c r="R18" t="n">
-        <v>6783815</v>
+        <v>6783881</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2385,39 +2451,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131674801</v>
+        <v>131674786</v>
       </c>
       <c r="B19" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2425,7 +2491,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2435,10 +2501,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459194</v>
+        <v>459276</v>
       </c>
       <c r="R19" t="n">
-        <v>6783791</v>
+        <v>6783842</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2497,32 +2563,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131674805</v>
+        <v>131674787</v>
       </c>
       <c r="B20" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2530,7 +2596,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2540,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459207</v>
+        <v>459258</v>
       </c>
       <c r="R20" t="n">
-        <v>6783784</v>
+        <v>6783805</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2602,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131674854</v>
+        <v>131674800</v>
       </c>
       <c r="B21" t="n">
-        <v>8460</v>
+        <v>57162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2613,30 +2679,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2646,10 +2711,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459227</v>
+        <v>459169</v>
       </c>
       <c r="R21" t="n">
-        <v>6783880</v>
+        <v>6783815</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2690,7 +2755,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2709,37 +2773,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131674847</v>
+        <v>131674801</v>
       </c>
       <c r="B22" t="n">
-        <v>79131</v>
+        <v>57162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2747,10 +2816,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459245</v>
+        <v>459194</v>
       </c>
       <c r="R22" t="n">
-        <v>6783875</v>
+        <v>6783791</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2791,7 +2860,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2810,45 +2878,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131674774</v>
+        <v>131674805</v>
       </c>
       <c r="B23" t="n">
-        <v>79963</v>
+        <v>57162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459202</v>
+        <v>459207</v>
       </c>
       <c r="R23" t="n">
-        <v>6783814</v>
+        <v>6783784</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2904,6 +2980,916 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131674854</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>459227</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6783880</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135298257</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58812</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>459213</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6783777</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135298259</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>459226</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6783798</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135298265</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>459250</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6783827</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135298266</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>459272</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6783876</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135298267</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>459276</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6783871</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131674847</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>459245</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6783875</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131674774</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>459202</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6783814</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7213-2026 artfynd.xlsx
+++ b/artfynd/A 7213-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298255</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298260</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1053,6 +1068,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298269</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674891</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674892</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674893</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674894</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1538,6 +1578,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674895</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674896</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674897</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1833,6 +1888,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674865</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674771</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2035,6 +2100,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674822</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674823</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2245,6 +2320,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674824</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2350,6 +2430,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674825</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2455,6 +2540,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674785</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2560,6 +2650,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674786</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2665,6 +2760,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674787</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2770,6 +2870,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674800</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2875,6 +2980,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674801</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2980,6 +3090,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674805</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3087,6 +3202,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674854</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3208,6 +3328,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298257</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3329,6 +3454,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298259</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3450,6 +3580,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298265</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3571,6 +3706,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298266</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3692,6 +3832,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298267</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3793,6 +3938,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674847</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3890,8 +4040,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674774</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 7213-2026 artfynd.xlsx
+++ b/artfynd/A 7213-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135298255</v>
       </c>
       <c r="B2" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>135298260</v>
       </c>
       <c r="B3" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>135298269</v>
       </c>
       <c r="B4" t="n">
-        <v>79405</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>135298257</v>
       </c>
       <c r="B25" t="n">
-        <v>58812</v>
+        <v>58817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>135298259</v>
       </c>
       <c r="B26" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>135298265</v>
       </c>
       <c r="B27" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>135298266</v>
       </c>
       <c r="B28" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>135298267</v>
       </c>
       <c r="B29" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 7213-2026 artfynd.xlsx
+++ b/artfynd/A 7213-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135298255</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>135298260</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>135298269</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
         <v>135298259</v>
       </c>
       <c r="B26" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>135298265</v>
       </c>
       <c r="B27" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>135298266</v>
       </c>
       <c r="B28" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>135298267</v>
       </c>
       <c r="B29" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 7213-2026 artfynd.xlsx
+++ b/artfynd/A 7213-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131674891</v>
+        <v>135298255</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459200</v>
+        <v>459206</v>
       </c>
       <c r="R2" t="n">
-        <v>6783838</v>
+        <v>6783780</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,69 +771,89 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674891</t>
+          <t>https://artportalen.se/Sighting/135298255</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131674892</v>
+        <v>135298260</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459218</v>
+        <v>459206</v>
       </c>
       <c r="R3" t="n">
-        <v>6783873</v>
+        <v>6783812</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +877,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -863,69 +903,89 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674892</t>
+          <t>https://artportalen.se/Sighting/135298260</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131674893</v>
+        <v>135298269</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skordmyrbäck, Dlr</t>
+          <t>Per-Larsmyr, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459231</v>
+        <v>459172</v>
       </c>
       <c r="R4" t="n">
-        <v>6783873</v>
+        <v>6783876</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +1009,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -965,28 +1035,48 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674893</t>
+          <t>https://artportalen.se/Sighting/135298269</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131674894</v>
+        <v>131674891</v>
       </c>
       <c r="B5" t="n">
         <v>79373</v>
@@ -1021,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459258</v>
+        <v>459200</v>
       </c>
       <c r="R5" t="n">
-        <v>6783870</v>
+        <v>6783838</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,13 +1172,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674894</t>
+          <t>https://artportalen.se/Sighting/131674891</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131674895</v>
+        <v>131674892</v>
       </c>
       <c r="B6" t="n">
         <v>79373</v>
@@ -1123,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459235</v>
+        <v>459218</v>
       </c>
       <c r="R6" t="n">
-        <v>6783794</v>
+        <v>6783873</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,13 +1274,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674895</t>
+          <t>https://artportalen.se/Sighting/131674892</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131674896</v>
+        <v>131674893</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1225,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459194</v>
+        <v>459231</v>
       </c>
       <c r="R7" t="n">
-        <v>6783789</v>
+        <v>6783873</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,13 +1376,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674896</t>
+          <t>https://artportalen.se/Sighting/131674893</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131674897</v>
+        <v>131674894</v>
       </c>
       <c r="B8" t="n">
         <v>79373</v>
@@ -1327,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459178</v>
+        <v>459258</v>
       </c>
       <c r="R8" t="n">
-        <v>6783796</v>
+        <v>6783870</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,54 +1478,51 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674897</t>
+          <t>https://artportalen.se/Sighting/131674894</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131674865</v>
+        <v>131674895</v>
       </c>
       <c r="B9" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459284</v>
+        <v>459235</v>
       </c>
       <c r="R9" t="n">
-        <v>6783888</v>
+        <v>6783794</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,7 +1563,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1488,44 +1574,44 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674865</t>
+          <t>https://artportalen.se/Sighting/131674895</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131674771</v>
+        <v>131674896</v>
       </c>
       <c r="B10" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459199</v>
+        <v>459194</v>
       </c>
       <c r="R10" t="n">
-        <v>6783825</v>
+        <v>6783789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,59 +1682,51 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674771</t>
+          <t>https://artportalen.se/Sighting/131674896</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131674822</v>
+        <v>131674897</v>
       </c>
       <c r="B11" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459276</v>
+        <v>459178</v>
       </c>
       <c r="R11" t="n">
-        <v>6783886</v>
+        <v>6783796</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1706,48 +1784,43 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674822</t>
+          <t>https://artportalen.se/Sighting/131674897</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131674823</v>
+        <v>131674865</v>
       </c>
       <c r="B12" t="n">
-        <v>57972</v>
+        <v>79130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1755,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459255</v>
+        <v>459284</v>
       </c>
       <c r="R12" t="n">
-        <v>6783871</v>
+        <v>6783888</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,6 +1872,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1810,65 +1884,57 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674823</t>
+          <t>https://artportalen.se/Sighting/131674865</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131674824</v>
+        <v>131674771</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459194</v>
+        <v>459199</v>
       </c>
       <c r="R13" t="n">
-        <v>6783789</v>
+        <v>6783825</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1926,13 +1992,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674824</t>
+          <t>https://artportalen.se/Sighting/131674771</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131674825</v>
+        <v>131674822</v>
       </c>
       <c r="B14" t="n">
         <v>57972</v>
@@ -1965,7 +2031,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1975,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459186</v>
+        <v>459276</v>
       </c>
       <c r="R14" t="n">
-        <v>6783788</v>
+        <v>6783886</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,33 +2102,33 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674825</t>
+          <t>https://artportalen.se/Sighting/131674822</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131674785</v>
+        <v>131674823</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2085,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459269</v>
+        <v>459255</v>
       </c>
       <c r="R15" t="n">
-        <v>6783881</v>
+        <v>6783871</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,39 +2206,39 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674785</t>
+          <t>https://artportalen.se/Sighting/131674823</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131674786</v>
+        <v>131674824</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2185,7 +2251,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2195,10 +2261,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459276</v>
+        <v>459194</v>
       </c>
       <c r="R16" t="n">
-        <v>6783842</v>
+        <v>6783789</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2256,33 +2322,33 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674786</t>
+          <t>https://artportalen.se/Sighting/131674824</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131674787</v>
+        <v>131674825</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2295,7 +2361,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2305,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459258</v>
+        <v>459186</v>
       </c>
       <c r="R17" t="n">
-        <v>6783805</v>
+        <v>6783788</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,38 +2432,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674787</t>
+          <t>https://artportalen.se/Sighting/131674825</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131674800</v>
+        <v>131674785</v>
       </c>
       <c r="B18" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2405,7 +2471,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2415,10 +2481,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459169</v>
+        <v>459269</v>
       </c>
       <c r="R18" t="n">
-        <v>6783815</v>
+        <v>6783881</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2470,44 +2536,44 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674800</t>
+          <t>https://artportalen.se/Sighting/131674785</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131674801</v>
+        <v>131674786</v>
       </c>
       <c r="B19" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2515,7 +2581,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2525,10 +2591,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>459194</v>
+        <v>459276</v>
       </c>
       <c r="R19" t="n">
-        <v>6783791</v>
+        <v>6783842</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2586,38 +2652,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674801</t>
+          <t>https://artportalen.se/Sighting/131674786</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131674805</v>
+        <v>131674787</v>
       </c>
       <c r="B20" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2625,7 +2691,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2635,10 +2701,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459207</v>
+        <v>459258</v>
       </c>
       <c r="R20" t="n">
-        <v>6783784</v>
+        <v>6783805</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,16 +2762,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674805</t>
+          <t>https://artportalen.se/Sighting/131674787</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131674854</v>
+        <v>131674800</v>
       </c>
       <c r="B21" t="n">
-        <v>8460</v>
+        <v>57162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2713,30 +2779,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2746,10 +2811,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459227</v>
+        <v>459169</v>
       </c>
       <c r="R21" t="n">
-        <v>6783880</v>
+        <v>6783815</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2790,7 +2855,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2808,43 +2872,48 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674854</t>
+          <t>https://artportalen.se/Sighting/131674800</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131674847</v>
+        <v>131674801</v>
       </c>
       <c r="B22" t="n">
-        <v>79131</v>
+        <v>57162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2852,10 +2921,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459245</v>
+        <v>459194</v>
       </c>
       <c r="R22" t="n">
-        <v>6783875</v>
+        <v>6783791</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2896,7 +2965,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2914,51 +2982,59 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131674847</t>
+          <t>https://artportalen.se/Sighting/131674801</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131674774</v>
+        <v>131674805</v>
       </c>
       <c r="B23" t="n">
-        <v>79963</v>
+        <v>57162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skordmyrbäck, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459202</v>
+        <v>459207</v>
       </c>
       <c r="R23" t="n">
-        <v>6783814</v>
+        <v>6783784</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3015,6 +3091,956 @@
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674805</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131674854</v>
+      </c>
+      <c r="B24" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>459227</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6783880</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674854</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135298257</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>459213</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6783777</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298257</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135298259</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>459226</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6783798</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298259</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135298265</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>459250</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6783827</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298265</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135298266</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>459272</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6783876</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298266</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135298267</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Per-Larsmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>459276</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6783871</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135298267</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131674847</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>459245</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6783875</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131674847</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131674774</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Skordmyrbäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>459202</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6783814</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131674774</t>
         </is>
@@ -3044,6 +4070,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7213-2026 artfynd.xlsx
+++ b/artfynd/A 7213-2026 artfynd.xlsx
@@ -3339,7 +3339,7 @@
         <v>135298259</v>
       </c>
       <c r="B26" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>135298265</v>
       </c>
       <c r="B27" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>135298266</v>
       </c>
       <c r="B28" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>135298267</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
